--- a/docs/namespace-registry/pds-namespace-registry.xlsx
+++ b/docs/namespace-registry/pds-namespace-registry.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.29" customWidth="1" min="1" max="1"/>
@@ -2229,17 +2229,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>dscovr</t>
+          <t>di</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>DSCOVR Mission</t>
+          <t>Deep Impact Primary and Extended Missions Dictionary</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>The DSCOVR Mission Data Dictionary contains classes and attributes that describe data products from the DSCOVR (Deep Space Climate Observatory) mission.</t>
+          <t>Mission dictionary for the primary Deep Impact (DI) mission as well as the two extended missions, Extrasolar Planet Observation and Characterization (EPOCh) and Deep Impact Extended Investigation (DIXI), known jointly as "EPOXI".</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -2249,32 +2249,32 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Bob Deen</t>
+          <t>Anne Raugh</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Bob.Deen at jpl.nasa.gov</t>
+          <t>araugh at umd.edu</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>45868</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>galileo</t>
+          <t>dscovr</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Galileo</t>
+          <t>DSCOVR Mission</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>The Galileo Mission Dictionary (galileo) contains classes, attributes and rules specific to the Galileo Mission and its instruments.</t>
+          <t>The DSCOVR Mission Data Dictionary contains classes and attributes that describe data products from the DSCOVR (Deep Space Climate Observatory) mission.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2284,32 +2284,32 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Jesse Stone; Beatrice Mueller</t>
+          <t>Bob Deen</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>jstone at psi.edu; mueller at psi.edu</t>
+          <t>Bob.Deen at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>45923</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>hisaki</t>
+          <t>galileo</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Hisaki (SPRINT-A)</t>
+          <t>Galileo</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Hisaki dictionary.</t>
+          <t>The Galileo Mission Dictionary (galileo) contains classes, attributes and rules specific to the Galileo Mission and its instruments.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2319,32 +2319,32 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Jesse Stone; Beatrice Mueller</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>jstone at psi.edu; mueller at psi.edu</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>45742</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>hst</t>
+          <t>hisaki</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Hubble Space Telescope</t>
+          <t>Hisaki (SPRINT-A)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Hubble Space Telescope Mission Dictionary.</t>
+          <t>Namespace for the Hisaki dictionary.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Matthew Tiscareno</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>matt at seti.org</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>44707</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>hyb2</t>
+          <t>hst</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Hayabusa 2</t>
+          <t>Hubble Space Telescope</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>This is the Hayabusa2 Mission Specific Data Dictionary.</t>
+          <t>Namespace for the Hubble Space Telescope Mission Dictionary.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Yukio Yamamoto</t>
+          <t>Matthew Tiscareno</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>yamamoto.yukio at jaxa.jp</t>
+          <t>matt at seti.org</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>44193</v>
+        <v>44707</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>iras</t>
+          <t>hyb2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Infrared Astronomical Satellite</t>
+          <t>Hayabusa 2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Infrared Astronomical Satellite.</t>
+          <t>This is the Hayabusa2 Mission Specific Data Dictionary.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2424,32 +2424,32 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Kristina Lopez</t>
+          <t>Yukio Yamamoto</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>klope at psi.edu</t>
+          <t>yamamoto.yukio at jaxa.jp</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>44735</v>
+        <v>44193</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>kplo</t>
+          <t>iras</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Korea Pathfinder Lunar Orbiter</t>
+          <t>Infrared Astronomical Satellite</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Korea Pathfinder Lunar Orbiter(KPLO).</t>
+          <t>Namespace for the Infrared Astronomical Satellite.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Eunhyeuk Kim</t>
+          <t>Kristina Lopez</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>eunhyeuk at kari.re.kr</t>
+          <t>klope at psi.edu</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>44426</v>
+        <v>44735</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>insight</t>
+          <t>kplo</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Korea Pathfinder Lunar Orbiter</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Insight dictionary.</t>
+          <t>Namespace for the Korea Pathfinder Lunar Orbiter(KPLO).</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Eunhyeuk Kim</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>eunhyeuk at kari.re.kr</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>42119</v>
+        <v>44426</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>ladee</t>
+          <t>insight</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>LADEE</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Atmospheres Node's LADEE dictionary.</t>
+          <t>Namespace for the Insight dictionary.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -2529,32 +2529,32 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Lyle Huber</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>lhuber at nmsu.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>41837</v>
+        <v>42119</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>lcross</t>
+          <t>ladee</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>LCROSS</t>
+          <t>LADEE</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the LCROSS dictionary.</t>
+          <t>Namespace for the Atmospheres Node's LADEE dictionary.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Lyle Huber</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>lhuber at nmsu.edu</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>45612</v>
+        <v>41837</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>lt</t>
+          <t>lcross</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Lunar Trailblazer</t>
+          <t>LCROSS</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Geo Node's Lunar Trailblazer dictionary.</t>
+          <t>Namespace for the LCROSS dictionary.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2599,32 +2599,32 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Susie Slavney</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>44608</v>
+        <v>45612</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>lucy</t>
+          <t>lt</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Lucy Mission</t>
+          <t>Lunar Trailblazer</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Lucy Mission Dictionary.</t>
+          <t>Namespace for the Geo Node's Lunar Trailblazer dictionary.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2634,32 +2634,32 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Michael Kelley</t>
+          <t>Susie Slavney</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>msk at astro.umd.edu</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>44957</v>
+        <v>44608</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>mars2020</t>
+          <t>lucy</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Mars 2020 Mission</t>
+          <t>Lucy Mission</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars2020 Mission Local Data Dictionary</t>
+          <t>Namespace for the Lucy Mission Dictionary.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2669,32 +2669,32 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Susie Slavney</t>
+          <t>Michael Kelley</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>msk at astro.umd.edu</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>44333</v>
+        <v>44957</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>mer</t>
+          <t>mars2020</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Mars Exploration Rovers</t>
+          <t>Mars 2020 Mission</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Exploration Rovers dictionary.</t>
+          <t>Namespace for the Mars2020 Mission Local Data Dictionary</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2713,23 +2713,23 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>43935</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>mgn</t>
+          <t>mer</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Magellan</t>
+          <t>Mars Exploration Rovers</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Magellan dictionary.</t>
+          <t>Namespace for the Mars Exploration Rovers dictionary.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -2739,32 +2739,32 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Susie Slavney</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>45146</v>
+        <v>43935</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>mgs</t>
+          <t>mgn</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Mars Global Surveyor</t>
+          <t>Magellan</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Global Surveyor dictionary.</t>
+          <t>Namespace for the Magellan dictionary.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2774,32 +2774,32 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>41600</v>
+        <v>45146</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>mmx</t>
+          <t>mgs</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Martian Moons eXploration</t>
+          <t>Mars Global Surveyor</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Martian Moons eXploration dictionary.</t>
+          <t>Namespace for the Mars Global Surveyor dictionary.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -2809,32 +2809,32 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>45742</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>mpf</t>
+          <t>mmx</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Mars Pathfinder</t>
+          <t>Martian Moons eXploration</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Pathfinder dictionary.</t>
+          <t>Namespace for the Martian Moons eXploration dictionary.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -2844,32 +2844,32 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>42220</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>msl</t>
+          <t>mpf</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Mars Science Laboratory</t>
+          <t>Mars Pathfinder</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Science Laboratory dictionary.</t>
+          <t>Namespace for the Mars Pathfinder dictionary.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2879,32 +2879,32 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>44951</v>
+        <v>42220</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>mvn</t>
+          <t>msl</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MAVEN</t>
+          <t>Mars Science Laboratory</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the PPI Node's MAVEN dictionary.</t>
+          <t>Namespace for the Mars Science Laboratory dictionary.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>42158</v>
+        <v>44951</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>mro</t>
+          <t>mvn</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Mars Reconnaissance Orbiter</t>
+          <t>MAVEN</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Reconnaissance Orbiter.</t>
+          <t>Namespace for the PPI Node's MAVEN dictionary.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>44833</v>
+        <v>42158</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>mro</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Near Earth Asteroid Rendezvous Mission</t>
+          <t>Mars Reconnaissance Orbiter</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Near Earth Asteroid Rendezvous Mission dictionary.</t>
+          <t>Namespace for the Mars Reconnaissance Orbiter.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2984,32 +2984,32 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Kristina Lopez</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>klopez at psi.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>44713</v>
+        <v>44833</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>neas</t>
+          <t>near</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Near Earth Asteroid Scout</t>
+          <t>Near Earth Asteroid Rendezvous Mission</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Near Earth Asteroid Scout dictionary.</t>
+          <t>Namespace for the Near Earth Asteroid Rendezvous Mission dictionary.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -3019,32 +3019,32 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Kristina Lopez</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>klopez at psi.edu</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>43871</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>neas</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>New Horizons Primary and Extended Missions</t>
+          <t>Near Earth Asteroid Scout</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the New Horizons Primary and Extended Missions dictionary.</t>
+          <t>Namespace for the Near Earth Asteroid Scout dictionary.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Adeline Gicquel</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>agicquel at umd.edu</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>44643</v>
+        <v>43871</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>ody</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>2001 Mars Odyssey</t>
+          <t>New Horizons Primary and Extended Missions</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the 2001 Mars Odyssey dictionary.</t>
+          <t>Namespace for the New Horizons Primary and Extended Missions dictionary.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3089,32 +3089,32 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Daniel Politte</t>
+          <t>Adeline Gicquel</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>politte at wunder.wustl.edu</t>
+          <t>agicquel at umd.edu</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>44713</v>
+        <v>44643</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>orex</t>
+          <t>ody</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OSIRIS-Rex</t>
+          <t>2001 Mars Odyssey</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the OSIRIS-Rex dictionary.</t>
+          <t>Namespace for the 2001 Mars Odyssey dictionary.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3124,32 +3124,32 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Daniel Politte</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>politte at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>41771</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>orex</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Mars Phoenix</t>
+          <t>OSIRIS-Rex</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>The Mars Phoenix Mission Dictionary (phoenix) contains classes and attributes specific to the Phoenix mission and its instruments.</t>
+          <t>Namespace for the OSIRIS-Rex dictionary.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3159,32 +3159,32 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>45966</v>
+        <v>41771</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>psyche</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Psyche mission</t>
+          <t>Mars Phoenix</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Psyche dictionary.</t>
+          <t>The Mars Phoenix Mission Dictionary (phoenix) contains classes and attributes specific to the Phoenix mission and its instruments.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3194,32 +3194,32 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>45014</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>slim</t>
+          <t>psyche</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Smart Lander for Investigating Moon</t>
+          <t>Psyche mission</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Smart Lander for Investigating Moon (SLIM) dictionary.</t>
+          <t>Namespace for the Psyche dictionary.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>45742</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>sln</t>
+          <t>slim</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Kaguya (SELENE)</t>
+          <t>Smart Lander for Investigating Moon</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Kaguya (SELENE) dictionary.</t>
+          <t>Namespace for the Smart Lander for Investigating Moon (SLIM) dictionary.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3279,17 +3279,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>vco</t>
+          <t>sln</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Venus Climate Orbiter Akatsuki Mission</t>
+          <t>Kaguya (SELENE)</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>The Venus Climate Orbiter Akatsuki Mission Local Data Dictionary</t>
+          <t>Namespace for the Kaguya (SELENE) dictionary.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3308,23 +3308,23 @@
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>45914</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>vg1</t>
+          <t>vco</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Voyager 1</t>
+          <t>Venus Climate Orbiter Akatsuki Mission</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager 1 Spacecraft dictionary.</t>
+          <t>The Venus Climate Orbiter Akatsuki Mission Local Data Dictionary</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3334,32 +3334,32 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>45203</v>
+        <v>45914</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>vg2</t>
+          <t>vg1</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Voyager 2</t>
+          <t>Voyager 1</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager 2 Spacrcraft dictionary.</t>
+          <t>Namespace for the Voyager 1 Spacecraft dictionary.</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3384,17 +3384,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>vgr</t>
+          <t>vg2</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Voyager</t>
+          <t>Voyager 2</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager Mission dictionary.</t>
+          <t>Namespace for the Voyager 2 Spacrcraft dictionary.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3404,32 +3404,32 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Matthew Tiscareno</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>matt at seti.org</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>44700</v>
+        <v>45203</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>vikinglander</t>
+          <t>vgr</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Viking Lander</t>
+          <t>Voyager</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>The Viking Lander mission dictionary contains classes and attributes specific to the Viking Lander mission and its instruments.</t>
+          <t>Namespace for the Voyager Mission dictionary.</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3439,32 +3439,32 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Matthew Tiscareno</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>jgward@wustl.edu</t>
+          <t>matt at seti.org</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>45489</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>viper</t>
+          <t>vikinglander</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Volatiles Investigating Polar Exploration Rover</t>
+          <t>Viking Lander</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>The VIPER mission dictionary contains classes and attributes specific to the VIPER mission and its instruments.</t>
+          <t>The Viking Lander mission dictionary contains classes and attributes specific to the Viking Lander mission and its instruments.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3474,32 +3474,32 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Madison Touran</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>mnhughes at wustl.edu</t>
+          <t>jgward@wustl.edu</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>45031</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>viper</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo</t>
+          <t>Volatiles Investigating Polar Exploration Rover</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo schema.</t>
+          <t>The VIPER mission dictionary contains classes and attributes specific to the VIPER mission and its instruments.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo Science Ground Segment</t>
+          <t>Madison Touran</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>smartinez at sciops.esa.int</t>
+          <t>mnhughes at wustl.edu</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
-        <v>43788</v>
+        <v>45031</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>bc_mtm_cam</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MCAM</t>
+          <t>BepiColombo</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MCAM schema.</t>
+          <t>Namespace for the BepiColombo schema.</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Mark.Bentley at esa.int</t>
+          <t>smartinez at sciops.esa.int</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
@@ -3559,17 +3559,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_bel</t>
+          <t>bc_mtm_cam</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo BELA</t>
+          <t>BepiColombo MCAM</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo BELA schema.</t>
+          <t>Namespace for the BepiColombo MCAM schema.</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3594,17 +3594,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_ber</t>
+          <t>bc_mpo_bel</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo BERM</t>
+          <t>BepiColombo BELA</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo BERM schema.</t>
+          <t>Namespace for the BepiColombo BELA schema.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3629,17 +3629,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_isa</t>
+          <t>bc_mpo_ber</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo ISA</t>
+          <t>BepiColombo BERM</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo ISA schema.</t>
+          <t>Namespace for the BepiColombo BERM schema.</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -3664,17 +3664,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mag</t>
+          <t>bc_mpo_isa</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MPO-MAG</t>
+          <t>BepiColombo ISA</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MPO-MAG schema.</t>
+          <t>Namespace for the BepiColombo ISA schema.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -3699,17 +3699,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mer</t>
+          <t>bc_mpo_mag</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MERTIS</t>
+          <t>BepiColombo MPO-MAG</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MERTIS schema.</t>
+          <t>Namespace for the BepiColombo MPO-MAG schema.</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -3734,17 +3734,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mgn</t>
+          <t>bc_mpo_mer</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MGNS</t>
+          <t>BepiColombo MERTIS</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MGNS schema.</t>
+          <t>Namespace for the BepiColombo MERTIS schema.</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mix</t>
+          <t>bc_mpo_mgn</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MIXS</t>
+          <t>BepiColombo MGNS</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MIXS schema.</t>
+          <t>Namespace for the BepiColombo MGNS schema.</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3804,17 +3804,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mre</t>
+          <t>bc_mpo_mix</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MORE</t>
+          <t>BepiColombo MIXS</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MORE schema.</t>
+          <t>Namespace for the BepiColombo MIXS schema.</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3839,17 +3839,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_phe</t>
+          <t>bc_mpo_mre</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo PHEBUS</t>
+          <t>BepiColombo MORE</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo PHEBUS schema.</t>
+          <t>Namespace for the BepiColombo MORE schema.</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -3874,17 +3874,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_srn</t>
+          <t>bc_mpo_phe</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SERENA</t>
+          <t>BepiColombo PHEBUS</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SERENA schema.</t>
+          <t>Namespace for the BepiColombo PHEBUS schema.</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_sim</t>
+          <t>bc_mpo_srn</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SIMBIO-SYS</t>
+          <t>BepiColombo SERENA</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SIMBIO-SYS  schema.</t>
+          <t>Namespace for the BepiColombo SERENA schema.</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -3944,17 +3944,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_six</t>
+          <t>bc_mpo_sim</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SIXS</t>
+          <t>BepiColombo SIMBIO-SYS</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SIXS  schema.</t>
+          <t>Namespace for the BepiColombo SIMBIO-SYS  schema.</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -3979,17 +3979,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_msasi</t>
+          <t>bc_mpo_six</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MSASI</t>
+          <t>BepiColombo SIXS</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MSASI schema.</t>
+          <t>Namespace for the BepiColombo SIXS  schema.</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -3999,32 +3999,32 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>BepiColombo Science Ground Segment</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>Mark.Bentley at esa.int</t>
         </is>
       </c>
       <c r="G104" s="4" t="n">
-        <v>45761</v>
+        <v>43788</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_pwi</t>
+          <t>bc_mmo_msasi</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo PWI</t>
+          <t>BepiColombo MSASI</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo PWI schema.</t>
+          <t>Namespace for the BepiColombo MSASI schema.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -4049,17 +4049,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mgf</t>
+          <t>bc_mmo_pwi</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MGF</t>
+          <t>BepiColombo PWI</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MGF schema.</t>
+          <t>Namespace for the BepiColombo PWI schema.</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -4084,17 +4084,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mppe</t>
+          <t>bc_mmo_mgf</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MPPE</t>
+          <t>BepiColombo MGF</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MPPE schema.</t>
+          <t>Namespace for the BepiColombo MGF schema.</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -4119,17 +4119,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mdm</t>
+          <t>bc_mmo_mppe</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MDM</t>
+          <t>BepiColombo MPPE</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MDM schema.</t>
+          <t>Namespace for the BepiColombo MPPE schema.</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -4154,17 +4154,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_spm</t>
+          <t>bc_mmo_mdm</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SPM</t>
+          <t>BepiColombo MDM</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SPM schema.</t>
+          <t>Namespace for the BepiColombo MDM schema.</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -4189,17 +4189,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>chan1</t>
+          <t>bc_mmo_spm</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>BepiColombo SPM</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Chandrayaan-1 mission dictionary</t>
+          <t>Namespace for the BepiColombo SPM schema.</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Susan Slavney</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G110" s="4" t="n">
-        <v>44111</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>em16</t>
+          <t>chan1</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ExoMars16</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 schema.</t>
+          <t>Chandrayaan-1 mission dictionary</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -4244,22 +4244,22 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>ExoMars16 Science Operations Centre</t>
+          <t>Susan Slavney</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G111" s="4" t="n">
-        <v>43788</v>
+        <v>44111</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_acs</t>
+          <t>em16</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 ACS Instrument schema.</t>
+          <t>Namespace for the ExoMars16 schema.</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>dcoia at sciops.esa.int</t>
+          <t>tlim at sciops.esa.int</t>
         </is>
       </c>
       <c r="G112" s="4" t="n">
@@ -4294,7 +4294,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_cas</t>
+          <t>em16_tgo_acs</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 CaSSIS Instrument schema.</t>
+          <t>Namespace for the ExoMars16 ACS Instrument schema.</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>dcoia at sciops.esa.int</t>
         </is>
       </c>
       <c r="G113" s="4" t="n">
@@ -4329,7 +4329,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_nmd</t>
+          <t>em16_tgo_cas</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 NOMAD Instrument schema.</t>
+          <t>Namespace for the ExoMars16 CaSSIS Instrument schema.</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_frd</t>
+          <t>em16_tgo_nmd</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 FREND Instrument schema.</t>
+          <t>Namespace for the ExoMars16 NOMAD Instrument schema.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>dcoia at sciops.esa.int</t>
+          <t>tlim at sciops.esa.int</t>
         </is>
       </c>
       <c r="G115" s="4" t="n">
@@ -4399,17 +4399,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>emrsp</t>
+          <t>em16_tgo_frd</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ExoMarsRSP</t>
+          <t>ExoMars16</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP mission schema.</t>
+          <t>Namespace for the ExoMars16 FREND Instrument schema.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>ExoMarsRSP Science Operations Centre</t>
+          <t>ExoMars16 Science Operations Centre</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>dcoia at sciops.esa.int</t>
         </is>
       </c>
       <c r="G116" s="4" t="n">
@@ -4434,7 +4434,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm</t>
+          <t>emrsp</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP Rover Host schema.</t>
+          <t>Namespace for the ExoMarsRSP mission schema.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_nav</t>
+          <t>emrsp_rm</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP NavCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP Rover Host schema.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -4504,7 +4504,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_loc</t>
+          <t>emrsp_rm_nav</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP LocCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP NavCam Instrument schema.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_pan</t>
+          <t>emrsp_rm_loc</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP PanCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP LocCam Instrument schema.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_ise</t>
+          <t>emrsp_rm_pan</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP ISEM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP PanCam Instrument schema.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_clu</t>
+          <t>emrsp_rm_ise</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP CLUPI Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP ISEM Instrument schema.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_wis</t>
+          <t>emrsp_rm_clu</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP WISDOM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP CLUPI Instrument schema.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_arm</t>
+          <t>emrsp_rm_wis</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP ADRON_RM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP WISDOM Instrument schema.</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mis</t>
+          <t>emrsp_rm_arm</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MaMISS Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP ADRON_RM Instrument schema.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4749,7 +4749,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mic</t>
+          <t>emrsp_rm_mis</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MicrOmega Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MaMISS Instrument schema.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mom</t>
+          <t>emrsp_rm_mic</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MOMA Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MicrOmega Instrument schema.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_rls</t>
+          <t>emrsp_rm_mom</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP RLS Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MOMA Instrument schema.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4854,17 +4854,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>juice</t>
+          <t>emrsp_rm_rls</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>JUICE mission</t>
+          <t>ExoMarsRSP</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE mission schema.</t>
+          <t>Namespace for the ExoMarsRSP RLS Instrument schema.</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4874,28 +4874,32 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>JUICE Science Operations Centre</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="n"/>
+          <t>ExoMarsRSP Science Operations Centre</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>tlim at sciops.esa.int</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
-        <v>45509</v>
+        <v>43788</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>juice_gala</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>JUICE GALA Instrument</t>
+          <t>JUICE mission</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE GALA Instrument schema.</t>
+          <t>Namespace for the JUICE mission schema.</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4916,17 +4920,17 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>juice_janus</t>
+          <t>juice_gala</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>JUICE JANUS Instrument</t>
+          <t>JUICE GALA Instrument</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JANUS Instrument schema.</t>
+          <t>Namespace for the JUICE GALA Instrument schema.</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -4947,17 +4951,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>juice_jmc</t>
+          <t>juice_janus</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>JUICE JMC Instrument</t>
+          <t>JUICE JANUS Instrument</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JMC Instrument schema.</t>
+          <t>Namespace for the JUICE JANUS Instrument schema.</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -4978,17 +4982,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>juice_majis</t>
+          <t>juice_jmc</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>JUICE MAJIS Instrument</t>
+          <t>JUICE JMC Instrument</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE MAJIS Instrument schema.</t>
+          <t>Namespace for the JUICE JMC Instrument schema.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -5009,17 +5013,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>juice_navcam</t>
+          <t>juice_majis</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>JUICE NAVCAM Instrument</t>
+          <t>JUICE MAJIS Instrument</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE NAVCAM Instrument schema.</t>
+          <t>Namespace for the JUICE MAJIS Instrument schema.</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -5040,17 +5044,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>juice_rime</t>
+          <t>juice_navcam</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>JUICE RIME Instrument</t>
+          <t>JUICE NAVCAM Instrument</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RIME Instrument schema.</t>
+          <t>Namespace for the JUICE NAVCAM Instrument schema.</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -5071,17 +5075,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>juice_swi</t>
+          <t>juice_rime</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>JUICE SWI Instrument</t>
+          <t>JUICE RIME Instrument</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE SWI Instrument schema.</t>
+          <t>Namespace for the JUICE RIME Instrument schema.</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -5102,17 +5106,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>juice_uvs</t>
+          <t>juice_swi</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>JUICE UVS Instrument</t>
+          <t>JUICE SWI Instrument</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE UVS Instrument schema.</t>
+          <t>Namespace for the JUICE SWI Instrument schema.</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -5133,17 +5137,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>juice_radem</t>
+          <t>juice_uvs</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>JUICE RADEM Instrument</t>
+          <t>JUICE UVS Instrument</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RADEM Instrument schema.</t>
+          <t>Namespace for the JUICE UVS Instrument schema.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -5164,17 +5168,17 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>juice_3gm</t>
+          <t>juice_radem</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>JUICE 3GM Instrument</t>
+          <t>JUICE RADEM Instrument</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE 3GM Instrument schema.</t>
+          <t>Namespace for the JUICE RADEM Instrument schema.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -5195,17 +5199,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>juice_haa</t>
+          <t>juice_3gm</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>JUICE HAA Instrument</t>
+          <t>JUICE 3GM Instrument</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE HAA Instrument schema.</t>
+          <t>Namespace for the JUICE 3GM Instrument schema.</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -5226,17 +5230,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>juice_jmag</t>
+          <t>juice_haa</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>JUICE JMAG Instrument</t>
+          <t>JUICE HAA Instrument</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JMAG Instrument schema.</t>
+          <t>Namespace for the JUICE HAA Instrument schema.</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -5257,17 +5261,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>juice_rpwi</t>
+          <t>juice_jmag</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>JUICE RPWI Instrument</t>
+          <t>JUICE JMAG Instrument</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RPWI Instrument schema.</t>
+          <t>Namespace for the JUICE JMAG Instrument schema.</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5288,17 +5292,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>juice_pephi</t>
+          <t>juice_rpwi</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>JUICE PEPHI Instrument</t>
+          <t>JUICE RPWI Instrument</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PEPHI Instrument schema.</t>
+          <t>Namespace for the JUICE RPWI Instrument schema.</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -5319,17 +5323,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>juice_peplo</t>
+          <t>juice_pephi</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>JUICE PEPLO Instrument</t>
+          <t>JUICE PEPHI Instrument</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PEPLO Instrument schema.</t>
+          <t>Namespace for the JUICE PEPHI Instrument schema.</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -5350,17 +5354,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>juice_pride</t>
+          <t>juice_peplo</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>JUICE PRIDE Instrument</t>
+          <t>JUICE PEPLO Instrument</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PRIDE Instrument schema.</t>
+          <t>Namespace for the JUICE PEPLO Instrument schema.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -5381,17 +5385,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>vex</t>
+          <t>juice_pride</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Venus Express Mission</t>
+          <t>JUICE PRIDE Instrument</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Venus Express Mission schema.</t>
+          <t>Namespace for the JUICE PRIDE Instrument schema.</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -5401,32 +5405,28 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Mark Bentley</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>Mark.Bentley at esa.int</t>
-        </is>
-      </c>
+          <t>JUICE Science Operations Centre</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n"/>
       <c r="G146" s="4" t="n">
-        <v>45715</v>
+        <v>45509</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>smart1</t>
+          <t>vex</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Small Missions for Advanced Research in Technology Mission</t>
+          <t>Venus Express Mission</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Small Missions for Advanced Research in Technology mission schema.</t>
+          <t>Namespace for the Venus Express Mission schema.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -5451,35 +5451,70 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
+          <t>smart1</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Small Missions for Advanced Research in Technology Mission</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Namespace for the Small Missions for Advanced Research in Technology mission schema.</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Mark Bentley</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Mark.Bentley at esa.int</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>45715</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
           <t>giotto</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>Giotto Mission</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>Namespace for the Giotto Mission schema.</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>Mark Bentley</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>Mark.Bentley at esa.int</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G149" s="4" t="n">
         <v>45715</v>
       </c>
     </row>

--- a/docs/namespace-registry/pds-namespace-registry.xlsx
+++ b/docs/namespace-registry/pds-namespace-registry.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.29" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -801,67 +801,67 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>epncore</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>EPNCore</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>This LDD contains the EPNcore dictionary, as defined in the IVOA specification, with few design adjustments.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Baptiste Cecconi</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>baptiste.cecconi at observatoiredeparis.psl.eu</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>46280</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>alt</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Alternate</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Namespace for the PPI Node's Alternate dictionary.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mafi</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>jmafi at igpp.ucla.edu</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>42118</v>
-      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ama</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Atmospheres Modeling Annex</t>
+          <t>Alternate</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>This LDD provides attributes appropriate to atmospheric modeling products that will reside in the Atmospheres Modeling Annex.</t>
+          <t>Namespace for the PPI Node's Alternate dictionary.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -871,32 +871,32 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Lyle Huber</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>lhuber at nmsu.edu</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>45680</v>
+        <v>42118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>atm</t>
+          <t>ama</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Atmosphere's Node</t>
+          <t>Atmospheres Modeling Annex</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Atmospheres node's dictionary.</t>
+          <t>This LDD provides attributes appropriate to atmospheric modeling products that will reside in the Atmospheres Modeling Annex.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -915,23 +915,23 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>41002</v>
+        <v>45680</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>av</t>
+          <t>atm</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Audio_Video</t>
+          <t>Atmosphere's Node</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The Audio_Video (AV) LDD contains metadata related to audio and video products that use Encoded_Audio or Encoded_Video. The metadata in this LDD is a subset of what is in the stream itself (usually in the form of EXIF/XMP tags), in order to facilitate searching using standard PDS tools. Thus only attributes likely to be useful for search are included here. The use of this LDD is optional but recommended for AV data.</t>
+          <t>Namespace for the Atmospheres node's dictionary.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -941,32 +941,32 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Bob Deen</t>
+          <t>Lyle Huber</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Bob.Deen at jpl.nasa.gov</t>
+          <t>lhuber at nmsu.edu</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>46150</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>cart</t>
+          <t>av</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Cartography</t>
+          <t>Audio_Video</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>The Cartography Dictionary contains classes, elements, attributes, and rules describing map projections, including both cartographic and lander related definitions and descriptions. The PDS Cartography dictionary is based on and utilizes the existing Federal Geographic Data Committee (FGDC) Content Standard for Digital Geospatial Metadata, with modifications and extensions applied by PDS as needed for planetary mapping application.</t>
+          <t>The Audio_Video (AV) LDD contains metadata related to audio and video products that use Encoded_Audio or Encoded_Video. The metadata in this LDD is a subset of what is in the stream itself (usually in the form of EXIF/XMP tags), in order to facilitate searching using standard PDS tools. Thus only attributes likely to be useful for search are included here. The use of this LDD is optional but recommended for AV data.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -976,32 +976,32 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Bob Deen</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>Bob.Deen at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>42299</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ctli</t>
+          <t>cart</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Common Type List Instrument</t>
+          <t>Cartography</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>The CTLI dictionary provides a set of type values for instruments for use in instrument context products.</t>
+          <t>The Cartography Dictionary contains classes, elements, attributes, and rules describing map projections, including both cartographic and lander related definitions and descriptions. The PDS Cartography dictionary is based on and utilizes the existing Federal Geographic Data Committee (FGDC) Content Standard for Digital Geospatial Metadata, with modifications and extensions applied by PDS as needed for planetary mapping application.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1011,32 +1011,32 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Lyle Huber</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>lhuber at nmsu.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>44329</v>
+        <v>42299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>disp</t>
+          <t>ctli</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Common Type List Instrument</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>The Display Dictionary contains classes, attributes, and rules for specifying how arrays (images) as stored, should be displayed to users. For example, defining the vertical display direction 'Bottom to Top' or horizontal direction 'Left to Right' and it can provide guidance on mapping multiband arrays for color display (red, green, and blue) or as a movie sequence (video).</t>
+          <t>The CTLI dictionary provides a set of type values for instruments for use in instrument context products.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1046,32 +1046,32 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Lyle Huber</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>lhuber at nmsu.edu</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>41435</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ebt</t>
+          <t>disp</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Earth-Based Telescope</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>This namespace will provide observing parameters, provenance, and geometry relevant to ground-based telescopes on Earth and for Earth-orbiting (or Lagrange point) telescopes</t>
+          <t>The Display Dictionary contains classes, attributes, and rules for specifying how arrays (images) as stored, should be displayed to users. For example, defining the vertical display direction 'Bottom to Top' or horizontal direction 'Left to Right' and it can provide guidance on mapping multiband arrays for color display (red, green, and blue) or as a movie sequence (video).</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1081,32 +1081,32 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Ben Hirsch</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>bhirsch1 at umd.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>44398</v>
+        <v>41435</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>ebt</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Geosciences</t>
+          <t>Earth-Based Telescope</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Geosciences node's dictionary.</t>
+          <t>This namespace will provide observing parameters, provenance, and geometry relevant to ground-based telescopes on Earth and for Earth-orbiting (or Lagrange point) telescopes</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1116,32 +1116,32 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Ben Hirsch</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>bhirsch1 at umd.edu</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>41002</v>
+        <v>44398</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>geom</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Geosciences</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>The Geometry Dictionary contains classes, attributes, and rules for specifying the geometry parameters associated with science observations.</t>
+          <t>Namespace for the Geosciences node's dictionary.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Edward Guinness, Mitchell Gordon</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>guinness at wunder.wustl.edu, mgordon@seti.org</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>42124</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>img</t>
+          <t>geom</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>The Imaging Dictionary contains classes, attributes, and rules for specifying the metadata associated with imaging and spectrometer data products.</t>
+          <t>The Geometry Dictionary contains classes, attributes, and rules for specifying the geometry parameters associated with science observations.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1186,32 +1186,32 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Edward Guinness, Mitchell Gordon</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>guinness at wunder.wustl.edu, mgordon@seti.org</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>41002</v>
+        <v>42124</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>img_surface</t>
+          <t>img</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Surface Imaging</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>The Surface Imaging Dictionary contains classes, attributes, and rules for specifying the metadata associated with imaging and spectrometer data products of surface missions.</t>
+          <t>The Imaging Dictionary contains classes, attributes, and rules for specifying the metadata associated with imaging and spectrometer data products.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1230,23 +1230,23 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>43734</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>img_surface</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Classifier</t>
+          <t>Surface Imaging</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Classifier Discipline Local Data Dictionary</t>
+          <t>The Surface Imaging Dictionary contains classes, attributes, and rules for specifying the metadata associated with imaging and spectrometer data products of surface missions.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1256,32 +1256,32 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Mike McAuley</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Michael.McAuley at jpl.nasa.gov</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>44333</v>
+        <v>43734</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>msn</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mission Information Commons</t>
+          <t>Machine Learning Classifier</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>The sub-directory for the Mission Information class namespace.</t>
+          <t>Machine Learning Classifier Discipline Local Data Dictionary</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Mike McAuley</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>Michael.McAuley at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>42650</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>msn_surface</t>
+          <t>msn</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Surface Mission Information</t>
+          <t>Mission Information Commons</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>The Surface Mission Dictionary contains classes, attributes, and rules for specifying metadata elements which are specific to the data products of surface missions but are common among multiple such missions.</t>
+          <t>The sub-directory for the Mission Information class namespace.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1335,23 +1335,23 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>43734</v>
+        <v>42650</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>msn_surface</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Multidimensional</t>
+          <t>Surface Mission Information</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>The Multi dictionary contains classes that describe the composition of multidimensional data consisting of Array (and Array subclass) data objects. It provides a way to associated data objects and align the objects in general multi-dimensional structures.</t>
+          <t>The Surface Mission Dictionary contains classes, attributes, and rules for specifying metadata elements which are specific to the data products of surface missions but are common among multiple such missions.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1361,32 +1361,32 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>44257</v>
+        <v>43734</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>naif</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Navigation and Ancillary Information Facility</t>
+          <t>Multidimensional</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the NAIF node's dictionary.</t>
+          <t>The Multi dictionary contains classes that describe the composition of multidimensional data consisting of Array (and Array subclass) data objects. It provides a way to associated data objects and align the objects in general multi-dimensional structures.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1396,32 +1396,32 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Boris Semenov</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Boris.V.Semenov at jpl.nasa.gov</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>41002</v>
+        <v>44257</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>nucspec</t>
+          <t>naif</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nuclear Spectroscopy</t>
+          <t>Navigation and Ancillary Information Facility</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>The Nuclear Spectroscopy dictionary provides classes, attributes, and rules for describing the circumstances surrounding nuclear spectroscopy observations.</t>
+          <t>Namespace for the NAIF node's dictionary.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Jesse Stone</t>
+          <t>Boris Semenov</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>jstone at psi.edu</t>
+          <t>Boris.V.Semenov at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>44110</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ops</t>
+          <t>nucspec</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PDS Operations</t>
+          <t>Nuclear Spectroscopy</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Operations metadata appended to PDS4 metadata in order to support PDS Core Services, such as the Registry.</t>
+          <t>The Nuclear Spectroscopy dictionary provides classes, attributes, and rules for describing the circumstances surrounding nuclear spectroscopy observations.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Sophia Conover</t>
+          <t>Jesse Stone</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>sophia.n.conover at jpl.nasa.gov</t>
+          <t>jstone at psi.edu</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>41002</v>
+        <v>44110</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>particle</t>
+          <t>ops</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Particle</t>
+          <t>PDS Operations</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>The Particle dictionary contains classes that describe the composition of multidimensional particle data consisting of Array (and Array subclass) data objects.</t>
+          <t>Operations metadata appended to PDS4 metadata in order to support PDS Core Services, such as the Registry.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1501,32 +1501,32 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Sophia Conover</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>sophia.n.conover at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>42118</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ppi</t>
+          <t>particle</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PPI</t>
+          <t>Particle</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the PPI node's dictionary.</t>
+          <t>The Particle dictionary contains classes that describe the composition of multidimensional particle data consisting of Array (and Array subclass) data objects.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1545,23 +1545,23 @@
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>41002</v>
+        <v>42118</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>proc</t>
+          <t>ppi</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Processing Information</t>
+          <t>PPI</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>The Processing_Information Dictionary contains detailed information regarding the history of processing performed on data product(s) in order to produce the current product.</t>
+          <t>Namespace for the PPI node's dictionary.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1571,32 +1571,32 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>43734</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>prov</t>
+          <t>proc</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Processing Information</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>The purpose of the "prov" LDD is to provide a PDS4 "Discipline_Area" insert for capturing provenance information.</t>
+          <t>The Processing_Information Dictionary contains detailed information regarding the history of processing performed on data product(s) in order to produce the current product.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1606,32 +1606,32 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Steve Hughes</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Steve.Hughes at jpl.nasa.gov</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>45924</v>
+        <v>43734</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>radar</t>
+          <t>prov</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Describes the circumstances surrounding radar observations.</t>
+          <t>The purpose of the "prov" LDD is to provide a PDS4 "Discipline_Area" insert for capturing provenance information.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1641,32 +1641,32 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Beatrice Mueller</t>
+          <t>Steve Hughes</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>mueller at psi.edu</t>
+          <t>Steve.Hughes at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>44489</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>rings</t>
+          <t>radar</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Rings</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>The Rings Dictionary contains classes supporting planetary ring observations including ring-specific geometric parameters.</t>
+          <t>Describes the circumstances surrounding radar observations.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1676,32 +1676,32 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Mitchel Gordon</t>
+          <t>Beatrice Mueller</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>mgordon at seti.org</t>
+          <t>mueller at psi.edu</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>41002</v>
+        <v>44489</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>rs</t>
+          <t>rings</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Radio Science</t>
+          <t>Rings</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Radio Science node's dictionary.</t>
+          <t>The Rings Dictionary contains classes supporting planetary ring observations including ring-specific geometric parameters.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Richard Simpson</t>
+          <t>Mitchel Gordon</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>radiosci at att.net</t>
+          <t>mgordon at seti.org</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -1726,17 +1726,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>sb</t>
+          <t>rs</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Small Bodies Node Dictionary</t>
+          <t>Radio Science</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>This dictionary will provide classes to support the documentation, support, discovery, and reuse of data from, by, and for small bodies research.</t>
+          <t>Namespace for the Radio Science node's dictionary.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1746,32 +1746,32 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Anne Raugh</t>
+          <t>Richard Simpson</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>araugh at umd.edu</t>
+          <t>radiosci at att.net</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>44943</v>
+        <v>41002</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>sp</t>
+          <t>sb</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Spectral</t>
+          <t>Small Bodies Node Dictionary</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>The Spectral (sp) Discipline Dictionary contains classes for defining the spectral bin characteristics (in wavelength, frequency, or wave number) of a data product.</t>
+          <t>This dictionary will provide classes to support the documentation, support, discovery, and reuse of data from, by, and for small bodies research.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1790,23 +1790,23 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>41589</v>
+        <v>44943</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>speclib</t>
+          <t>sp</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Spectral Library</t>
+          <t>Spectral</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>The Spectral Library Data Dictionary defines the metadata terms that describe laboratory spectral measurements, including classification of the samples measured.</t>
+          <t>The Spectral (sp) Discipline Dictionary contains classes for defining the spectral bin characteristics (in wavelength, frequency, or wave number) of a data product.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Susie Slavney</t>
+          <t>Anne Raugh</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>araugh at umd.edu</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>42870</v>
+        <v>41589</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>speclib</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Survey</t>
+          <t>Spectral Library</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>The Survey dictionary provides classes, attributes, and rules for describing the circumstances surrounding sky survey observations.</t>
+          <t>The Spectral Library Data Dictionary defines the metadata terms that describe laboratory spectral measurements, including classification of the samples measured.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1851,115 +1851,115 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Jesse Stone</t>
+          <t>Susie Slavney</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>jstone at psi.edu</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>44110</v>
+        <v>42870</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>The Survey dictionary provides classes, attributes, and rules for describing the circumstances surrounding sky survey observations.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Jesse Stone</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>jstone at psi.edu</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>44110</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>wave</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Wave</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>The Wave dictionary contains classes that describe the composition of multidimensional wave data consisting of Array (and Array subclass) data objects.</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Joseph Mafi</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>42118</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>apex</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>APEX Mission</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>The APEX Mission Dictionary (apex) contains classes, attributes and rules specific to the APEX mission.</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Carol Neese</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>neese at psi.edu</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>46127</v>
-      </c>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>apex</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>APEX Mission</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>The Apollo Mission Dictionary (apollo) contains classes, attributes and rules specific to the Apollo missions and their instruments.</t>
+          <t>The APEX Mission Dictionary (apex) contains classes, attributes and rules specific to the APEX mission.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -1969,32 +1969,32 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>44791</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>asl</t>
+          <t>apollo</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Mars Missions Analogue Sample Library</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Mars Missions Analogue Sample Library metadata</t>
+          <t>The Apollo Mission Dictionary (apollo) contains classes, attributes and rules specific to the Apollo missions and their instruments.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2004,32 +2004,32 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Thomas Cornet</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>thomas.cornet at esa.int</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>46071</v>
+        <v>44791</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>bopps</t>
+          <t>asl</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Balloon Observation Platform for Planetary Science</t>
+          <t>Mars Missions Analogue Sample Library</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BOPPS dictionary.</t>
+          <t>Mars Missions Analogue Sample Library metadata</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Anne Raugh</t>
+          <t>Thomas Cornet</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>araugh at umd.edu</t>
+          <t>thomas.cornet at esa.int</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>42089</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>clementine</t>
+          <t>bopps</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Clementine</t>
+          <t>Balloon Observation Platform for Planetary Science</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>The Clementine mission dictionary contains a class with attributes specific to the Deep Space Program Science Experiment, including the Clementine orbiter and its instruments. This dictionary was created for the migration of Clementine data products from PDS3 to PDS4 by Million Concepts (contact M. St. Clair).</t>
+          <t>Namespace for the BOPPS dictionary.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2074,32 +2074,32 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Anne Raugh</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>araugh at umd.edu</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>44329</v>
+        <v>42089</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>clipper</t>
+          <t>clementine</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>clipper</t>
+          <t>Clementine</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>The Europa Clipper mission dictionary contains classes that describe aspects of the Clipper mission and related instruments.</t>
+          <t>The Clementine mission dictionary contains a class with attributes specific to the Deep Space Program Science Experiment, including the Clementine orbiter and its instruments. This dictionary was created for the migration of Clementine data products from PDS3 to PDS4 by Million Concepts (contact M. St. Clair).</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2118,23 +2118,23 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>44385</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>clps</t>
+          <t>clipper</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>clps</t>
+          <t>clipper</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>The Commercial Lunar Payload Services Mission Dictionary (clps) contains classes, attributes and rules specific to the CLPS missions and their instruments.</t>
+          <t>The Europa Clipper mission dictionary contains classes that describe aspects of the Clipper mission and related instruments.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2144,32 +2144,32 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>45013</v>
+        <v>44385</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>cots_camera</t>
+          <t>clps</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>COTS Camera</t>
+          <t>clps</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>The COTS Camera Mission Dictionary (cots_camera) contains classes, attributes and rules specific to commercial off-the-shelf camera instruments.</t>
+          <t>The Commercial Lunar Payload Services Mission Dictionary (clps) contains classes, attributes and rules specific to the CLPS missions and their instruments.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2179,32 +2179,32 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Bob Deen</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Bob.Deen at jpl.nasa.gov</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>46127</v>
+        <v>45013</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>dart</t>
+          <t>cots_camera</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>dart</t>
+          <t>COTS Camera</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>This namespace provides classes specific to the NASA DART mission and, potentially, the concurrent LICIACube mission.</t>
+          <t>The COTS Camera Mission Dictionary (cots_camera) contains classes, attributes and rules specific to commercial off-the-shelf camera instruments.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -2214,32 +2214,32 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Ben Hirsch</t>
+          <t>Bob Deen</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>bhirsch1 at umd.edu</t>
+          <t>Bob.Deen at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>44426</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>di</t>
+          <t>dart</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Deep Impact Primary and Extended Missions Dictionary</t>
+          <t>dart</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Mission dictionary for the primary Deep Impact (DI) mission as well as the two extended missions, Extrasolar Planet Observation and Characterization (EPOCh) and Deep Impact Extended Investigation (DIXI), known jointly as "EPOXI".</t>
+          <t>This namespace provides classes specific to the NASA DART mission and, potentially, the concurrent LICIACube mission.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -2249,32 +2249,32 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Anne Raugh</t>
+          <t>Ben Hirsch</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>araugh at umd.edu</t>
+          <t>bhirsch1 at umd.edu</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>46286</v>
+        <v>44426</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>dscovr</t>
+          <t>di</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>DSCOVR Mission</t>
+          <t>Deep Impact Primary and Extended Missions Dictionary</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>The DSCOVR Mission Data Dictionary contains classes and attributes that describe data products from the DSCOVR (Deep Space Climate Observatory) mission.</t>
+          <t>Mission dictionary for the primary Deep Impact (DI) mission as well as the two extended missions, Extrasolar Planet Observation and Characterization (EPOCh) and Deep Impact Extended Investigation (DIXI), known jointly as "EPOXI".</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2284,32 +2284,32 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Bob Deen</t>
+          <t>Anne Raugh</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Bob.Deen at jpl.nasa.gov</t>
+          <t>araugh at umd.edu</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>45868</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>galileo</t>
+          <t>dscovr</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Galileo</t>
+          <t>DSCOVR Mission</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>The Galileo Mission Dictionary (galileo) contains classes, attributes and rules specific to the Galileo Mission and its instruments.</t>
+          <t>The DSCOVR Mission Data Dictionary contains classes and attributes that describe data products from the DSCOVR (Deep Space Climate Observatory) mission.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2319,32 +2319,32 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Jesse Stone; Beatrice Mueller</t>
+          <t>Bob Deen</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>jstone at psi.edu; mueller at psi.edu</t>
+          <t>Bob.Deen at jpl.nasa.gov</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>45923</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>hisaki</t>
+          <t>galileo</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Hisaki (SPRINT-A)</t>
+          <t>Galileo</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Hisaki dictionary.</t>
+          <t>The Galileo Mission Dictionary (galileo) contains classes, attributes and rules specific to the Galileo Mission and its instruments.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Jesse Stone; Beatrice Mueller</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>jstone at psi.edu; mueller at psi.edu</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>45742</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>hst</t>
+          <t>hisaki</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Hubble Space Telescope</t>
+          <t>Hisaki (SPRINT-A)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Hubble Space Telescope Mission Dictionary.</t>
+          <t>Namespace for the Hisaki dictionary.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Matthew Tiscareno</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>matt at seti.org</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>44707</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>hyb2</t>
+          <t>hst</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Hayabusa 2</t>
+          <t>Hubble Space Telescope</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>This is the Hayabusa2 Mission Specific Data Dictionary.</t>
+          <t>Namespace for the Hubble Space Telescope Mission Dictionary.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2424,32 +2424,32 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Yukio Yamamoto</t>
+          <t>Matthew Tiscareno</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>yamamoto.yukio at jaxa.jp</t>
+          <t>matt at seti.org</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>44193</v>
+        <v>44707</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>iras</t>
+          <t>hyb2</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Infrared Astronomical Satellite</t>
+          <t>Hayabusa 2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Infrared Astronomical Satellite.</t>
+          <t>This is the Hayabusa2 Mission Specific Data Dictionary.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Kristina Lopez</t>
+          <t>Yukio Yamamoto</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>klope at psi.edu</t>
+          <t>yamamoto.yukio at jaxa.jp</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>44735</v>
+        <v>44193</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>kplo</t>
+          <t>iras</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Korea Pathfinder Lunar Orbiter</t>
+          <t>Infrared Astronomical Satellite</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Korea Pathfinder Lunar Orbiter(KPLO).</t>
+          <t>Namespace for the Infrared Astronomical Satellite.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Eunhyeuk Kim</t>
+          <t>Kristina Lopez</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>eunhyeuk at kari.re.kr</t>
+          <t>klope at psi.edu</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>44426</v>
+        <v>44735</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>insight</t>
+          <t>kplo</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Korea Pathfinder Lunar Orbiter</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Insight dictionary.</t>
+          <t>Namespace for the Korea Pathfinder Lunar Orbiter(KPLO).</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -2529,32 +2529,32 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Eunhyeuk Kim</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>eunhyeuk at kari.re.kr</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>42119</v>
+        <v>44426</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>ladee</t>
+          <t>insight</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>LADEE</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Atmospheres Node's LADEE dictionary.</t>
+          <t>Namespace for the Insight dictionary.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Lyle Huber</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>lhuber at nmsu.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>41837</v>
+        <v>42119</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>lcross</t>
+          <t>ladee</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>LCROSS</t>
+          <t>LADEE</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the LCROSS dictionary.</t>
+          <t>Namespace for the Atmospheres Node's LADEE dictionary.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2599,32 +2599,32 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Lyle Huber</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>lhuber at nmsu.edu</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>45612</v>
+        <v>41837</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>lt</t>
+          <t>lcross</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Lunar Trailblazer</t>
+          <t>LCROSS</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Geo Node's Lunar Trailblazer dictionary.</t>
+          <t>Namespace for the LCROSS dictionary.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2634,32 +2634,32 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Susie Slavney</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>44608</v>
+        <v>45612</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>lucy</t>
+          <t>lt</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Lucy Mission</t>
+          <t>Lunar Trailblazer</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Lucy Mission Dictionary.</t>
+          <t>Namespace for the Geo Node's Lunar Trailblazer dictionary.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2669,32 +2669,32 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Michael Kelley</t>
+          <t>Susie Slavney</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>msk at astro.umd.edu</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>44957</v>
+        <v>44608</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>mars2020</t>
+          <t>lucy</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Mars 2020 Mission</t>
+          <t>Lucy Mission</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars2020 Mission Local Data Dictionary</t>
+          <t>Namespace for the Lucy Mission Dictionary.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2704,32 +2704,32 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Susie Slavney</t>
+          <t>Michael Kelley</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>msk at astro.umd.edu</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>44333</v>
+        <v>44957</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>mer</t>
+          <t>mars2020</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Mars Exploration Rovers</t>
+          <t>Mars 2020 Mission</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Exploration Rovers dictionary.</t>
+          <t>Namespace for the Mars2020 Mission Local Data Dictionary</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -2748,23 +2748,23 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>43935</v>
+        <v>44333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>mgn</t>
+          <t>mer</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Magellan</t>
+          <t>Mars Exploration Rovers</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Magellan dictionary.</t>
+          <t>Namespace for the Mars Exploration Rovers dictionary.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2774,32 +2774,32 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Susie Slavney</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>45146</v>
+        <v>43935</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>mgs</t>
+          <t>mgn</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Mars Global Surveyor</t>
+          <t>Magellan</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Global Surveyor dictionary.</t>
+          <t>Namespace for the Magellan dictionary.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -2809,32 +2809,32 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>41600</v>
+        <v>45146</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>mmx</t>
+          <t>mgs</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Martian Moons eXploration</t>
+          <t>Mars Global Surveyor</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Martian Moons eXploration dictionary.</t>
+          <t>Namespace for the Mars Global Surveyor dictionary.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -2844,32 +2844,32 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>45742</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>mpf</t>
+          <t>mmx</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Mars Pathfinder</t>
+          <t>Martian Moons eXploration</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Pathfinder dictionary.</t>
+          <t>Namespace for the Martian Moons eXploration dictionary.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2879,32 +2879,32 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Trent Hare</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>thare at usgs.gov</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>42220</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>msl</t>
+          <t>mpf</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Mars Science Laboratory</t>
+          <t>Mars Pathfinder</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Science Laboratory dictionary.</t>
+          <t>Namespace for the Mars Pathfinder dictionary.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Trent Hare</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>thare at usgs.gov</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>44951</v>
+        <v>42220</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>mvn</t>
+          <t>msl</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>MAVEN</t>
+          <t>Mars Science Laboratory</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the PPI Node's MAVEN dictionary.</t>
+          <t>Namespace for the Mars Science Laboratory dictionary.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>42158</v>
+        <v>44951</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>mro</t>
+          <t>mvn</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Mars Reconnaissance Orbiter</t>
+          <t>MAVEN</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Mars Reconnaissance Orbiter.</t>
+          <t>Namespace for the PPI Node's MAVEN dictionary.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2984,32 +2984,32 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>44833</v>
+        <v>42158</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>mro</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Near Earth Asteroid Rendezvous Mission</t>
+          <t>Mars Reconnaissance Orbiter</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Near Earth Asteroid Rendezvous Mission dictionary.</t>
+          <t>Namespace for the Mars Reconnaissance Orbiter.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -3019,32 +3019,32 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Kristina Lopez</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>klopez at psi.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>44713</v>
+        <v>44833</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>neas</t>
+          <t>near</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Near Earth Asteroid Scout</t>
+          <t>Near Earth Asteroid Rendezvous Mission</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Near Earth Asteroid Scout dictionary.</t>
+          <t>Namespace for the Near Earth Asteroid Rendezvous Mission dictionary.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Kristina Lopez</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>klopez at psi.edu</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>43871</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>neas</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>New Horizons Primary and Extended Missions</t>
+          <t>Near Earth Asteroid Scout</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the New Horizons Primary and Extended Missions dictionary.</t>
+          <t>Namespace for the Near Earth Asteroid Scout dictionary.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3089,32 +3089,32 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Adeline Gicquel</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>agicquel at umd.edu</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>44643</v>
+        <v>43871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>ody</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>2001 Mars Odyssey</t>
+          <t>New Horizons Primary and Extended Missions</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the 2001 Mars Odyssey dictionary.</t>
+          <t>Namespace for the New Horizons Primary and Extended Missions dictionary.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3124,32 +3124,32 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Daniel Politte</t>
+          <t>Adeline Gicquel</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>politte at wunder.wustl.edu</t>
+          <t>agicquel at umd.edu</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>44713</v>
+        <v>44643</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>orex</t>
+          <t>ody</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>OSIRIS-Rex</t>
+          <t>2001 Mars Odyssey</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the OSIRIS-Rex dictionary.</t>
+          <t>Namespace for the 2001 Mars Odyssey dictionary.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3159,32 +3159,32 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Daniel Politte</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>politte at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>41771</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>orex</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Mars Phoenix</t>
+          <t>OSIRIS-Rex</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>The Mars Phoenix Mission Dictionary (phoenix) contains classes and attributes specific to the Phoenix mission and its instruments.</t>
+          <t>Namespace for the OSIRIS-Rex dictionary.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3194,32 +3194,32 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>jgward at wustl.edu</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>45966</v>
+        <v>41771</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>psyche</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Psyche mission</t>
+          <t>Mars Phoenix</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Psyche dictionary.</t>
+          <t>The Mars Phoenix Mission Dictionary (phoenix) contains classes and attributes specific to the Phoenix mission and its instruments.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Carol Neese</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>neese at psi.edu</t>
+          <t>jgward at wustl.edu</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>45014</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>slim</t>
+          <t>psyche</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Smart Lander for Investigating Moon</t>
+          <t>Psyche mission</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Smart Lander for Investigating Moon (SLIM) dictionary.</t>
+          <t>Namespace for the Psyche dictionary.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3264,32 +3264,32 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>Carol Neese</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>neese at psi.edu</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>45742</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>sln</t>
+          <t>slim</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Kaguya (SELENE)</t>
+          <t>Smart Lander for Investigating Moon</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Kaguya (SELENE) dictionary.</t>
+          <t>Namespace for the Smart Lander for Investigating Moon (SLIM) dictionary.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3314,17 +3314,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>vco</t>
+          <t>sln</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Venus Climate Orbiter Akatsuki Mission</t>
+          <t>Kaguya (SELENE)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>The Venus Climate Orbiter Akatsuki Mission Local Data Dictionary</t>
+          <t>Namespace for the Kaguya (SELENE) dictionary.</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3343,23 +3343,23 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>45914</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>vg1</t>
+          <t>vco</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Voyager 1</t>
+          <t>Venus Climate Orbiter Akatsuki Mission</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager 1 Spacecraft dictionary.</t>
+          <t>The Venus Climate Orbiter Akatsuki Mission Local Data Dictionary</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3369,32 +3369,32 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mafi</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>jmafi at igpp.ucla.edu</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>45203</v>
+        <v>45914</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>vg2</t>
+          <t>vg1</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Voyager 2</t>
+          <t>Voyager 1</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager 2 Spacrcraft dictionary.</t>
+          <t>Namespace for the Voyager 1 Spacecraft dictionary.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3419,17 +3419,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>vgr</t>
+          <t>vg2</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Voyager</t>
+          <t>Voyager 2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Voyager Mission dictionary.</t>
+          <t>Namespace for the Voyager 2 Spacrcraft dictionary.</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3439,32 +3439,32 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Matthew Tiscareno</t>
+          <t>Joseph Mafi</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>matt at seti.org</t>
+          <t>jmafi at igpp.ucla.edu</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>44700</v>
+        <v>45203</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>vikinglander</t>
+          <t>vgr</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Viking Lander</t>
+          <t>Voyager</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>The Viking Lander mission dictionary contains classes and attributes specific to the Viking Lander mission and its instruments.</t>
+          <t>Namespace for the Voyager Mission dictionary.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3474,32 +3474,32 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Ward</t>
+          <t>Matthew Tiscareno</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>jgward@wustl.edu</t>
+          <t>matt at seti.org</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>45489</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>viper</t>
+          <t>vikinglander</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Volatiles Investigating Polar Exploration Rover</t>
+          <t>Viking Lander</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>The VIPER mission dictionary contains classes and attributes specific to the VIPER mission and its instruments.</t>
+          <t>The Viking Lander mission dictionary contains classes and attributes specific to the Viking Lander mission and its instruments.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Madison Touran</t>
+          <t>Jennifer Ward</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>mnhughes at wustl.edu</t>
+          <t>jgward@wustl.edu</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
-        <v>45031</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>viper</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo</t>
+          <t>Volatiles Investigating Polar Exploration Rover</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo schema.</t>
+          <t>The VIPER mission dictionary contains classes and attributes specific to the VIPER mission and its instruments.</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo Science Ground Segment</t>
+          <t>Madison Touran</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>smartinez at sciops.esa.int</t>
+          <t>mnhughes at wustl.edu</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>43788</v>
+        <v>45031</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>bc_mtm_cam</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MCAM</t>
+          <t>BepiColombo</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MCAM schema.</t>
+          <t>Namespace for the BepiColombo schema.</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Mark.Bentley at esa.int</t>
+          <t>smartinez at sciops.esa.int</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
@@ -3594,17 +3594,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_bel</t>
+          <t>bc_mtm_cam</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo BELA</t>
+          <t>BepiColombo MCAM</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo BELA schema.</t>
+          <t>Namespace for the BepiColombo MCAM schema.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3629,17 +3629,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_ber</t>
+          <t>bc_mpo_bel</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo BERM</t>
+          <t>BepiColombo BELA</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo BERM schema.</t>
+          <t>Namespace for the BepiColombo BELA schema.</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -3664,17 +3664,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_isa</t>
+          <t>bc_mpo_ber</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo ISA</t>
+          <t>BepiColombo BERM</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo ISA schema.</t>
+          <t>Namespace for the BepiColombo BERM schema.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -3699,17 +3699,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mag</t>
+          <t>bc_mpo_isa</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MPO-MAG</t>
+          <t>BepiColombo ISA</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MPO-MAG schema.</t>
+          <t>Namespace for the BepiColombo ISA schema.</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -3734,17 +3734,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mer</t>
+          <t>bc_mpo_mag</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MERTIS</t>
+          <t>BepiColombo MPO-MAG</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MERTIS schema.</t>
+          <t>Namespace for the BepiColombo MPO-MAG schema.</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mgn</t>
+          <t>bc_mpo_mer</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MGNS</t>
+          <t>BepiColombo MERTIS</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MGNS schema.</t>
+          <t>Namespace for the BepiColombo MERTIS schema.</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3804,17 +3804,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mix</t>
+          <t>bc_mpo_mgn</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MIXS</t>
+          <t>BepiColombo MGNS</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MIXS schema.</t>
+          <t>Namespace for the BepiColombo MGNS schema.</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3839,17 +3839,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_mre</t>
+          <t>bc_mpo_mix</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MORE</t>
+          <t>BepiColombo MIXS</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MORE schema.</t>
+          <t>Namespace for the BepiColombo MIXS schema.</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -3874,17 +3874,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_phe</t>
+          <t>bc_mpo_mre</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo PHEBUS</t>
+          <t>BepiColombo MORE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo PHEBUS schema.</t>
+          <t>Namespace for the BepiColombo MORE schema.</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_srn</t>
+          <t>bc_mpo_phe</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SERENA</t>
+          <t>BepiColombo PHEBUS</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SERENA schema.</t>
+          <t>Namespace for the BepiColombo PHEBUS schema.</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -3944,17 +3944,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_sim</t>
+          <t>bc_mpo_srn</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SIMBIO-SYS</t>
+          <t>BepiColombo SERENA</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SIMBIO-SYS  schema.</t>
+          <t>Namespace for the BepiColombo SERENA schema.</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -3979,17 +3979,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>bc_mpo_six</t>
+          <t>bc_mpo_sim</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SIXS</t>
+          <t>BepiColombo SIMBIO-SYS</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SIXS  schema.</t>
+          <t>Namespace for the BepiColombo SIMBIO-SYS  schema.</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -4014,17 +4014,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_msasi</t>
+          <t>bc_mpo_six</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MSASI</t>
+          <t>BepiColombo SIXS</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MSASI schema.</t>
+          <t>Namespace for the BepiColombo SIXS  schema.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -4034,32 +4034,32 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Shin-ya Murakami</t>
+          <t>BepiColombo Science Ground Segment</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>murakami.shinya at jaxa.jp</t>
+          <t>Mark.Bentley at esa.int</t>
         </is>
       </c>
       <c r="G105" s="4" t="n">
-        <v>45761</v>
+        <v>43788</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_pwi</t>
+          <t>bc_mmo_msasi</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo PWI</t>
+          <t>BepiColombo MSASI</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo PWI schema.</t>
+          <t>Namespace for the BepiColombo MSASI schema.</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -4084,17 +4084,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mgf</t>
+          <t>bc_mmo_pwi</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MGF</t>
+          <t>BepiColombo PWI</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MGF schema.</t>
+          <t>Namespace for the BepiColombo PWI schema.</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -4119,17 +4119,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mppe</t>
+          <t>bc_mmo_mgf</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MPPE</t>
+          <t>BepiColombo MGF</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MPPE schema.</t>
+          <t>Namespace for the BepiColombo MGF schema.</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -4154,17 +4154,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_mdm</t>
+          <t>bc_mmo_mppe</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo MDM</t>
+          <t>BepiColombo MPPE</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo MDM schema.</t>
+          <t>Namespace for the BepiColombo MPPE schema.</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -4189,17 +4189,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>bc_mmo_spm</t>
+          <t>bc_mmo_mdm</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>BepiColombo SPM</t>
+          <t>BepiColombo MDM</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the BepiColombo SPM schema.</t>
+          <t>Namespace for the BepiColombo MDM schema.</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -4224,17 +4224,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>chan1</t>
+          <t>bc_mmo_spm</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>BepiColombo SPM</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Chandrayaan-1 mission dictionary</t>
+          <t>Namespace for the BepiColombo SPM schema.</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -4244,32 +4244,32 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Susan Slavney</t>
+          <t>Shin-ya Murakami</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>slavney at wunder.wustl.edu</t>
+          <t>murakami.shinya at jaxa.jp</t>
         </is>
       </c>
       <c r="G111" s="4" t="n">
-        <v>44111</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>em16</t>
+          <t>chan1</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ExoMars16</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 schema.</t>
+          <t>Chandrayaan-1 mission dictionary</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>ExoMars16 Science Operations Centre</t>
+          <t>Susan Slavney</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>slavney at wunder.wustl.edu</t>
         </is>
       </c>
       <c r="G112" s="4" t="n">
-        <v>43788</v>
+        <v>44111</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_acs</t>
+          <t>em16</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 ACS Instrument schema.</t>
+          <t>Namespace for the ExoMars16 schema.</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>dcoia at sciops.esa.int</t>
+          <t>tlim at sciops.esa.int</t>
         </is>
       </c>
       <c r="G113" s="4" t="n">
@@ -4329,7 +4329,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_cas</t>
+          <t>em16_tgo_acs</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 CaSSIS Instrument schema.</t>
+          <t>Namespace for the ExoMars16 ACS Instrument schema.</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>dcoia at sciops.esa.int</t>
         </is>
       </c>
       <c r="G114" s="4" t="n">
@@ -4364,7 +4364,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_nmd</t>
+          <t>em16_tgo_cas</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 NOMAD Instrument schema.</t>
+          <t>Namespace for the ExoMars16 CaSSIS Instrument schema.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>em16_tgo_frd</t>
+          <t>em16_tgo_nmd</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMars16 FREND Instrument schema.</t>
+          <t>Namespace for the ExoMars16 NOMAD Instrument schema.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>dcoia at sciops.esa.int</t>
+          <t>tlim at sciops.esa.int</t>
         </is>
       </c>
       <c r="G116" s="4" t="n">
@@ -4434,17 +4434,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>emrsp</t>
+          <t>em16_tgo_frd</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ExoMarsRSP</t>
+          <t>ExoMars16</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP mission schema.</t>
+          <t>Namespace for the ExoMars16 FREND Instrument schema.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>ExoMarsRSP Science Operations Centre</t>
+          <t>ExoMars16 Science Operations Centre</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>tlim at sciops.esa.int</t>
+          <t>dcoia at sciops.esa.int</t>
         </is>
       </c>
       <c r="G117" s="4" t="n">
@@ -4469,7 +4469,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm</t>
+          <t>emrsp</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP Rover Host schema.</t>
+          <t>Namespace for the ExoMarsRSP mission schema.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -4504,7 +4504,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_nav</t>
+          <t>emrsp_rm</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP NavCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP Rover Host schema.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_loc</t>
+          <t>emrsp_rm_nav</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP LocCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP NavCam Instrument schema.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_pan</t>
+          <t>emrsp_rm_loc</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP PanCam Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP LocCam Instrument schema.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_ise</t>
+          <t>emrsp_rm_pan</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP ISEM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP PanCam Instrument schema.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_clu</t>
+          <t>emrsp_rm_ise</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP CLUPI Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP ISEM Instrument schema.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_wis</t>
+          <t>emrsp_rm_clu</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP WISDOM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP CLUPI Instrument schema.</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_arm</t>
+          <t>emrsp_rm_wis</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP ADRON_RM Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP WISDOM Instrument schema.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4749,7 +4749,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mis</t>
+          <t>emrsp_rm_arm</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MaMISS Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP ADRON_RM Instrument schema.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mic</t>
+          <t>emrsp_rm_mis</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MicrOmega Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MaMISS Instrument schema.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_mom</t>
+          <t>emrsp_rm_mic</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP MOMA Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MicrOmega Instrument schema.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>emrsp_rm_rls</t>
+          <t>emrsp_rm_mom</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the ExoMarsRSP RLS Instrument schema.</t>
+          <t>Namespace for the ExoMarsRSP MOMA Instrument schema.</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4889,17 +4889,17 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>juice</t>
+          <t>emrsp_rm_rls</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>JUICE mission</t>
+          <t>ExoMarsRSP</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE mission schema.</t>
+          <t>Namespace for the ExoMarsRSP RLS Instrument schema.</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4909,28 +4909,32 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>JUICE Science Operations Centre</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n"/>
+          <t>ExoMarsRSP Science Operations Centre</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>tlim at sciops.esa.int</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
-        <v>45509</v>
+        <v>43788</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>juice_gala</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>JUICE GALA Instrument</t>
+          <t>JUICE mission</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE GALA Instrument schema.</t>
+          <t>Namespace for the JUICE mission schema.</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -4951,17 +4955,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>juice_janus</t>
+          <t>juice_gala</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>JUICE JANUS Instrument</t>
+          <t>JUICE GALA Instrument</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JANUS Instrument schema.</t>
+          <t>Namespace for the JUICE GALA Instrument schema.</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -4982,17 +4986,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>juice_jmc</t>
+          <t>juice_janus</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>JUICE JMC Instrument</t>
+          <t>JUICE JANUS Instrument</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JMC Instrument schema.</t>
+          <t>Namespace for the JUICE JANUS Instrument schema.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -5013,17 +5017,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>juice_majis</t>
+          <t>juice_jmc</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>JUICE MAJIS Instrument</t>
+          <t>JUICE JMC Instrument</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE MAJIS Instrument schema.</t>
+          <t>Namespace for the JUICE JMC Instrument schema.</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -5044,17 +5048,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>juice_navcam</t>
+          <t>juice_majis</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>JUICE NAVCAM Instrument</t>
+          <t>JUICE MAJIS Instrument</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE NAVCAM Instrument schema.</t>
+          <t>Namespace for the JUICE MAJIS Instrument schema.</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -5075,17 +5079,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>juice_rime</t>
+          <t>juice_navcam</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>JUICE RIME Instrument</t>
+          <t>JUICE NAVCAM Instrument</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RIME Instrument schema.</t>
+          <t>Namespace for the JUICE NAVCAM Instrument schema.</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -5106,17 +5110,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>juice_swi</t>
+          <t>juice_rime</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>JUICE SWI Instrument</t>
+          <t>JUICE RIME Instrument</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE SWI Instrument schema.</t>
+          <t>Namespace for the JUICE RIME Instrument schema.</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -5137,17 +5141,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>juice_uvs</t>
+          <t>juice_swi</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>JUICE UVS Instrument</t>
+          <t>JUICE SWI Instrument</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE UVS Instrument schema.</t>
+          <t>Namespace for the JUICE SWI Instrument schema.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -5168,17 +5172,17 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>juice_radem</t>
+          <t>juice_uvs</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>JUICE RADEM Instrument</t>
+          <t>JUICE UVS Instrument</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RADEM Instrument schema.</t>
+          <t>Namespace for the JUICE UVS Instrument schema.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -5199,17 +5203,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>juice_3gm</t>
+          <t>juice_radem</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>JUICE 3GM Instrument</t>
+          <t>JUICE RADEM Instrument</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE 3GM Instrument schema.</t>
+          <t>Namespace for the JUICE RADEM Instrument schema.</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -5230,17 +5234,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>juice_haa</t>
+          <t>juice_3gm</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>JUICE HAA Instrument</t>
+          <t>JUICE 3GM Instrument</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE HAA Instrument schema.</t>
+          <t>Namespace for the JUICE 3GM Instrument schema.</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -5261,17 +5265,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>juice_jmag</t>
+          <t>juice_haa</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>JUICE JMAG Instrument</t>
+          <t>JUICE HAA Instrument</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE JMAG Instrument schema.</t>
+          <t>Namespace for the JUICE HAA Instrument schema.</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5292,17 +5296,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>juice_rpwi</t>
+          <t>juice_jmag</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>JUICE RPWI Instrument</t>
+          <t>JUICE JMAG Instrument</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE RPWI Instrument schema.</t>
+          <t>Namespace for the JUICE JMAG Instrument schema.</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -5323,17 +5327,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>juice_pephi</t>
+          <t>juice_rpwi</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>JUICE PEPHI Instrument</t>
+          <t>JUICE RPWI Instrument</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PEPHI Instrument schema.</t>
+          <t>Namespace for the JUICE RPWI Instrument schema.</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -5354,17 +5358,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>juice_peplo</t>
+          <t>juice_pephi</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>JUICE PEPLO Instrument</t>
+          <t>JUICE PEPHI Instrument</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PEPLO Instrument schema.</t>
+          <t>Namespace for the JUICE PEPHI Instrument schema.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -5385,17 +5389,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>juice_pride</t>
+          <t>juice_peplo</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>JUICE PRIDE Instrument</t>
+          <t>JUICE PEPLO Instrument</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the JUICE PRIDE Instrument schema.</t>
+          <t>Namespace for the JUICE PEPLO Instrument schema.</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -5416,17 +5420,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>vex</t>
+          <t>juice_pride</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Venus Express Mission</t>
+          <t>JUICE PRIDE Instrument</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Venus Express Mission schema.</t>
+          <t>Namespace for the JUICE PRIDE Instrument schema.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -5436,32 +5440,28 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Mark Bentley</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>Mark.Bentley at esa.int</t>
-        </is>
-      </c>
+          <t>JUICE Science Operations Centre</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n"/>
       <c r="G147" s="4" t="n">
-        <v>45715</v>
+        <v>45509</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>smart1</t>
+          <t>vex</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Small Missions for Advanced Research in Technology Mission</t>
+          <t>Venus Express Mission</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Namespace for the Small Missions for Advanced Research in Technology mission schema.</t>
+          <t>Namespace for the Venus Express Mission schema.</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -5486,35 +5486,70 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
+          <t>smart1</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Small Missions for Advanced Research in Technology Mission</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Namespace for the Small Missions for Advanced Research in Technology mission schema.</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Mark Bentley</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Mark.Bentley at esa.int</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>45715</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
           <t>giotto</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>Giotto Mission</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>Namespace for the Giotto Mission schema.</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>Mark Bentley</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>Mark.Bentley at esa.int</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G150" s="4" t="n">
         <v>45715</v>
       </c>
     </row>
